--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_159_R16.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_159_R16.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.559</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2827</v>
+        <v>-0.1891</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2763</v>
+        <v>1.1755</v>
       </c>
       <c r="G2" t="n">
         <v>0.152</v>
@@ -610,13 +610,13 @@
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.1386</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4129</v>
+        <v>-0.0589</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2983</v>
+        <v>0.1975</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>D. WASHINGTON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1543</v>
+        <v>-0.5797</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3797</v>
+        <v>-0.5716</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5339</v>
+        <v>-0.0081</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8987000000000001</v>
+        <v>0.4582</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3336</v>
+        <v>1.606</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4349</v>
+        <v>-1.1477</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0497</v>
+        <v>1.8523</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9024</v>
+        <v>2.679</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1472</v>
+        <v>-0.8267</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1509</v>
+        <v>-1.3941</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5688</v>
+        <v>-1.073</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5821</v>
+        <v>-0.3211</v>
       </c>
       <c r="P3" t="n">
         <v>-0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3195</v>
+        <v>-2.5515</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2555</v>
+        <v>-0.3626</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1098</v>
+        <v>-0.4086</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3654</v>
+        <v>0.0459</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0722</v>
+        <v>0.2525</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. WASHINGTON</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8149</v>
+        <v>-0.6866</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5716</v>
+        <v>-0.6156</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2433</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4582</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>1.606</v>
+        <v>1.3336</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1477</v>
+        <v>-0.4349</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8523</v>
+        <v>2.0497</v>
       </c>
       <c r="K4" t="n">
-        <v>2.679</v>
+        <v>1.9024</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8267</v>
+        <v>0.1472</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3941</v>
+        <v>-1.1509</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.073</v>
+        <v>-0.5688</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3211</v>
+        <v>-0.5821</v>
       </c>
       <c r="P4" t="n">
         <v>-0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.5515</v>
+        <v>-2.3195</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5979</v>
+        <v>0.4147</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4086</v>
+        <v>-0.3457</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1893</v>
+        <v>0.7604</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2525</v>
+        <v>-1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>V. MARINKOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.2683</v>
+        <v>-1.7842</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6232</v>
+        <v>-2.8292</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6452</v>
+        <v>1.045</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6768999999999999</v>
+        <v>-0.9099</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8054</v>
+        <v>-1.6361</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4822</v>
+        <v>0.7262</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9576</v>
+        <v>0.3625</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6792</v>
+        <v>-1.3171</v>
       </c>
       <c r="L6" t="n">
-        <v>2.2784</v>
+        <v>1.6796</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2807</v>
+        <v>-1.2724</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4845</v>
+        <v>-0.319</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7961</v>
+        <v>-0.9534</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.7834</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.871</v>
+        <v>-2.5515</v>
       </c>
       <c r="R6" t="n">
         <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.234</v>
+        <v>-0.9465</v>
       </c>
       <c r="T6" t="n">
         <v>-0.782</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.452</v>
+        <v>-0.1645</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2791</v>
+        <v>-1.8314</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2579</v>
+        <v>-1.6232</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0212</v>
+        <v>-0.2083</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.3698</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3289</v>
+        <v>-0.8054</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.041</v>
+        <v>1.4822</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3933</v>
+        <v>2.9576</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3592</v>
+        <v>0.6792</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.0341</v>
+        <v>2.2784</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9765</v>
+        <v>-2.2807</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9696</v>
+        <v>-1.4845</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0069</v>
+        <v>-0.7961</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3917</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.232</v>
+        <v>-4.871</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3009</v>
+        <v>-0.7971</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.782</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3317</v>
+        <v>-0.0151</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. MARINKOVIC</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4899</v>
+        <v>-2.565</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8292</v>
+        <v>-2.3758</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3392</v>
+        <v>-0.1892</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9099</v>
+        <v>-3.3698</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6361</v>
+        <v>-1.3289</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7262</v>
+        <v>-2.041</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3625</v>
+        <v>-1.3933</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3171</v>
+        <v>-0.3592</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6796</v>
+        <v>-1.0341</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2724</v>
+        <v>-1.9765</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.319</v>
+        <v>-0.9696</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9534</v>
+        <v>-1.0069</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6522</v>
+        <v>-0.5869</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.782</v>
+        <v>-0.7506</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8702</v>
+        <v>0.1637</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5717</v>
+        <v>-2.7555</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3601</v>
+        <v>-2.0063</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2116</v>
+        <v>-0.7493</v>
       </c>
       <c r="G9" t="n">
         <v>0.8528</v>
@@ -1156,13 +1156,13 @@
         <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.123</v>
+        <v>-0.3068</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9709</v>
+        <v>-0.617</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8479</v>
+        <v>0.3102</v>
       </c>
       <c r="V9" t="n">
         <v>-1.214</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8253</v>
+        <v>-3.6401</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2416</v>
+        <v>-4.1236</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4163</v>
+        <v>0.4835</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2461</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7415</v>
+        <v>-0.5564</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5975</v>
+        <v>-0.4795</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1441</v>
+        <v>-0.0769</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6778999999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9309</v>
+        <v>-4.6107</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.9417</v>
+        <v>-5.5879</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0108</v>
+        <v>0.9772</v>
       </c>
       <c r="G11" t="n">
         <v>-1.272</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.3233</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9709</v>
+        <v>-0.617</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3273</v>
+        <v>0.2937</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1351,7 +1351,7 @@
         <v>-20.858</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0783</v>
+        <v>2.0784</v>
       </c>
       <c r="G12" t="n">
         <v>-5.628500000000001</v>
@@ -1360,13 +1360,13 @@
         <v>-4.8259</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8025999999999998</v>
+        <v>-0.8025999999999995</v>
       </c>
       <c r="J12" t="n">
         <v>5.577799999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>1.8645</v>
+        <v>1.864500000000001</v>
       </c>
       <c r="L12" t="n">
         <v>3.713</v>
@@ -1390,16 +1390,16 @@
         <v>13.9174</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.5584</v>
+        <v>-3.5583</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.9908</v>
+        <v>-4.9907</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4324</v>
+        <v>1.4323</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3147</v>
+        <v>-0.3146999999999999</v>
       </c>
       <c r="W12" t="n">
         <v>1.7501</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.671099999999999</v>
+        <v>8.349500000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0046</v>
+        <v>4.1789</v>
       </c>
       <c r="F13" t="n">
-        <v>3.6665</v>
+        <v>4.1706</v>
       </c>
       <c r="G13" t="n">
         <v>5.4884</v>
@@ -1468,13 +1468,13 @@
         <v>3.7112</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0952</v>
+        <v>0.7736</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8575</v>
+        <v>0.0318</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2377</v>
+        <v>0.7418</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.608</v>
+        <v>4.1635</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9607</v>
+        <v>1.3146</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6473</v>
+        <v>2.849</v>
       </c>
       <c r="G14" t="n">
         <v>1.2209</v>
@@ -1546,13 +1546,13 @@
         <v>3.0154</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3962</v>
+        <v>0.1592</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5895</v>
+        <v>-0.2357</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1933</v>
+        <v>0.3949</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3571</v>
+        <v>3.2892</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2836</v>
+        <v>1.0477</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0735</v>
+        <v>2.2415</v>
       </c>
       <c r="G15" t="n">
         <v>1.755</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2104</v>
+        <v>0.1426</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1968</v>
+        <v>-0.0391</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0136</v>
+        <v>0.1817</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8437</v>
+        <v>3.0967</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7783</v>
+        <v>-0.4244</v>
       </c>
       <c r="F16" t="n">
-        <v>3.622</v>
+        <v>3.5212</v>
       </c>
       <c r="G16" t="n">
         <v>1.7849</v>
@@ -1702,13 +1702,13 @@
         <v>2.5515</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1489</v>
+        <v>0.402</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5895</v>
+        <v>-0.2357</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7385</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>0.6778999999999999</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4677</v>
+        <v>1.8286</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7056</v>
+        <v>0.4697</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7622</v>
+        <v>1.3589</v>
       </c>
       <c r="G17" t="n">
         <v>0.3453</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5709</v>
+        <v>0.9318</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5034</v>
+        <v>0.2675</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0675</v>
+        <v>0.6642</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9696</v>
+        <v>1.532</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6604</v>
+        <v>0.4245</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3092</v>
+        <v>1.1076</v>
       </c>
       <c r="G18" t="n">
         <v>0.1017</v>
@@ -1858,13 +1858,13 @@
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1747</v>
+        <v>0.7371</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5034</v>
+        <v>0.2675</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6713</v>
+        <v>0.4696</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9304</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0661</v>
+        <v>0.8544</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7244</v>
+        <v>-0.1548</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7905</v>
+        <v>1.0092</v>
       </c>
       <c r="G19" t="n">
-        <v>1.9937</v>
+        <v>1.2697</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5185</v>
+        <v>-0.0888</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4752</v>
+        <v>1.3585</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0297</v>
+        <v>1.4526</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9193</v>
+        <v>0.8269</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1104</v>
+        <v>0.6257</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.036</v>
+        <v>-0.1829</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4008</v>
+        <v>-0.9157</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3648</v>
+        <v>0.7328</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>-2.5515</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6291</v>
+        <v>-0.6319</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3541</v>
+        <v>-0.6642</v>
       </c>
       <c r="U19" t="n">
-        <v>0.275</v>
+        <v>0.0323</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3247</v>
+        <v>1.6083</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7886</v>
+        <v>1.6083</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1548</v>
+        <v>-1.0783</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7067</v>
+        <v>1.7905</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2697</v>
+        <v>1.9937</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0888</v>
+        <v>1.5185</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3585</v>
+        <v>0.4752</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4526</v>
+        <v>2.0297</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8269</v>
+        <v>1.9193</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6257</v>
+        <v>0.1104</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1829</v>
+        <v>-0.036</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9157</v>
+        <v>-0.4008</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7328</v>
+        <v>0.3648</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.5515</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9344</v>
+        <v>0.2752</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6642</v>
+        <v>0.0002</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2702</v>
+        <v>0.275</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6083</v>
+        <v>-1.3247</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6083</v>
+        <v>-0.7886</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0357</v>
+        <v>-0.749</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9647</v>
+        <v>-1.6109</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9291</v>
+        <v>0.8618</v>
       </c>
       <c r="G21" t="n">
         <v>-3.8364</v>
@@ -2092,13 +2092,13 @@
         <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0369</v>
+        <v>0.2497</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6405</v>
+        <v>-0.2867</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6036</v>
+        <v>0.5364</v>
       </c>
       <c r="V21" t="n">
         <v>1.214</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0921</v>
+        <v>-1.158</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3236</v>
+        <v>-1.8518</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2315</v>
+        <v>0.6938</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7688</v>
@@ -2170,13 +2170,13 @@
         <v>2.0876</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3725</v>
+        <v>0.3066</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7231</v>
+        <v>-0.2513</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0956</v>
+        <v>0.5579</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6279</v>
+        <v>-3.1396</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7475</v>
+        <v>-4.3936</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1195</v>
+        <v>1.254</v>
       </c>
       <c r="G23" t="n">
         <v>-3.7258</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2759</v>
+        <v>0.2124</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6405</v>
+        <v>-0.2867</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3646</v>
+        <v>0.4991</v>
       </c>
       <c r="V23" t="n">
         <v>0.1418</v>
@@ -2284,10 +2284,10 @@
         <v>18.7795</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.078399999999999</v>
+        <v>-2.0784</v>
       </c>
       <c r="F24" t="n">
-        <v>20.858</v>
+        <v>20.8581</v>
       </c>
       <c r="G24" t="n">
         <v>5.6286</v>
@@ -2329,7 +2329,7 @@
         <v>3.5583</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.4321</v>
+        <v>-1.4324</v>
       </c>
       <c r="U24" t="n">
         <v>4.9905</v>
